--- a/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（删除）-测试用例.xlsx
+++ b/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（删除）-测试用例.xlsx
@@ -1052,7 +1052,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4">
         <v>2</v>
@@ -1081,7 +1081,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="4">
         <v>2</v>
@@ -1107,7 +1107,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
@@ -1133,7 +1133,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4">
         <v>2</v>
@@ -1159,7 +1159,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4">
         <v>2</v>
@@ -1185,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4">
         <v>2</v>
@@ -1211,7 +1211,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4">
         <v>2</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4">
         <v>2</v>
@@ -1263,7 +1263,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4">
         <v>2</v>
@@ -1289,7 +1289,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -1315,7 +1315,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4">
         <v>2</v>
@@ -1341,7 +1341,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
@@ -1367,7 +1367,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4">
         <v>2</v>
@@ -1393,7 +1393,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="4">
         <v>2</v>
@@ -1419,7 +1419,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4">
         <v>2</v>
@@ -1445,7 +1445,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="4">
         <v>2</v>
@@ -1471,7 +1471,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="4">
         <v>2</v>
@@ -1497,7 +1497,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" s="4">
         <v>2</v>
@@ -1523,7 +1523,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="4">
         <v>2</v>
@@ -1549,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="E22" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4">
         <v>2</v>
@@ -1575,7 +1575,7 @@
         <v>2</v>
       </c>
       <c r="E23" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
@@ -1601,7 +1601,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="4">
         <v>2</v>
@@ -1627,7 +1627,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="4">
         <v>2</v>
